--- a/PROCEDURE/03-tableau-de-synthese-E5.xlsx
+++ b/PROCEDURE/03-tableau-de-synthese-E5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\COURS\SIO2\BLOC1\01- E4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentinvautier/Documents/GitHub/PORTFOLIO-E5/PROCEDURE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91117FCE-859B-46B8-B07A-B6151D3433F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25E0E1D7-120E-174C-ACCA-FB60D275E499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="57">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -195,18 +195,9 @@
     <t>15/01/25 au 15/01/25</t>
   </si>
   <si>
-    <t>Participation à un projet réseau client : audit, besoins et schéma d'infrastructure</t>
-  </si>
-  <si>
-    <t>03/03/25 au 30/04/25</t>
-  </si>
-  <si>
     <t>Rédaction d'une procédure interne à destination de l'équipe</t>
   </si>
   <si>
-    <t>01/04/25 au 01/04/25</t>
-  </si>
-  <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
@@ -228,7 +219,17 @@
     <t>Installation et administration d'un serveur DHCP sous Debian</t>
   </si>
   <si>
-    <t>18/03/26 au 20/03/26</t>
+    <t>18/03/25 au 20/03/25</t>
+  </si>
+  <si>
+    <t>2024-2026</t>
+  </si>
+  <si>
+    <t>Configuration Réseau :
+VLANs, DHCP, Routage, VTP et Sécurité</t>
+  </si>
+  <si>
+    <t>Participation à un projet technique</t>
   </si>
 </sst>
 </file>
@@ -238,7 +239,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -306,11 +307,13 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
@@ -324,12 +327,6 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -831,9 +828,87 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -858,86 +933,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1248,70 +1245,70 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ81"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="22.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="70.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="22.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="21" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="16384" width="10.85546875" style="1"/>
+    <col min="9" max="43" width="11.5" customWidth="1"/>
+    <col min="44" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="19"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1">
-      <c r="A2" s="19" t="s">
+      <c r="H1" s="34"/>
+    </row>
+    <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="26" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="27"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="53"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
       <c r="F4" s="12" t="s">
         <v>6</v>
       </c>
@@ -1322,23 +1319,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1">
-      <c r="A6" s="28" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="41" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1360,25 +1357,25 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="306" customHeight="1" thickBot="1">
-      <c r="A7" s="29"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="53" t="s">
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="306" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="33"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="31" t="s">
         <v>23</v>
       </c>
       <c r="I7"/>
@@ -1417,17 +1414,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="31"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="37"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1464,21 +1461,21 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A9" s="52" t="s">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1515,16 +1512,16 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A10" s="52" t="s">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="27" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="20" t="s">
         <v>27</v>
       </c>
       <c r="F10" s="14"/>
@@ -1566,11 +1563,11 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A11" s="52" t="s">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="28" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="14"/>
@@ -1578,7 +1575,7 @@
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I11"/>
@@ -1617,20 +1614,20 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A12" s="52" t="s">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
       <c r="H12" s="15"/>
       <c r="I12"/>
       <c r="J12"/>
@@ -1668,20 +1665,20 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A13" s="52" t="s">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="42"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="20"/>
       <c r="H13" s="15"/>
       <c r="I13"/>
       <c r="J13"/>
@@ -1719,20 +1716,20 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A14" s="52" t="s">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="42" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="20" t="s">
         <v>27</v>
       </c>
       <c r="H14" s="15"/>
@@ -1772,14 +1769,22 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="14"/>
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+      <c r="G15" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="H15" s="15"/>
       <c r="I15"/>
       <c r="J15"/>
@@ -1817,14 +1822,20 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="B16" s="8"/>
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="54">
+        <v>45575</v>
+      </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
+      <c r="G16" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="H16" s="15"/>
       <c r="I16"/>
       <c r="J16"/>
@@ -1862,7 +1873,7 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="9"/>
       <c r="B17" s="8"/>
       <c r="C17" s="14"/>
@@ -1907,7 +1918,7 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
       <c r="B18" s="8"/>
       <c r="C18" s="14"/>
@@ -1952,17 +1963,17 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18">
-      <c r="A19" s="32" t="s">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
+      <c r="A19" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="34"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1999,21 +2010,21 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A20" s="41" t="s">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="42" t="s">
+      <c r="C20" s="21"/>
+      <c r="D20" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2050,23 +2061,23 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A21" s="41" t="s">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="44"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2103,21 +2114,21 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A22" s="41" t="s">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="42" t="s">
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="44"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2154,21 +2165,21 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="49.5" customHeight="1">
-      <c r="A23" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="42" t="s">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="43"/>
-      <c r="H23" s="44"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2205,21 +2216,14 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="43.5" customHeight="1">
-      <c r="A24" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="19"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2256,7 +2260,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="9"/>
       <c r="B25" s="8"/>
       <c r="C25" s="14"/>
@@ -2301,7 +2305,7 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="9"/>
       <c r="B26" s="8"/>
       <c r="C26" s="14"/>
@@ -2346,17 +2350,17 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="18">
-      <c r="A27" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="34"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.15">
+      <c r="A27" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2393,21 +2397,21 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A28" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="42" t="s">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H28" s="44"/>
+      <c r="H28" s="22"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2444,21 +2448,21 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A29" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="42" t="s">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H29" s="44"/>
+      <c r="H29" s="22"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2495,23 +2499,23 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="53.25" customHeight="1">
-      <c r="A30" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="42" t="s">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="42" t="s">
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H30" s="44"/>
+      <c r="H30" s="22"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2548,23 +2552,21 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="48.75" customHeight="1">
-      <c r="A31" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="47" t="s">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="44"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="22"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2601,7 +2603,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="14"/>
@@ -2646,7 +2648,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="9"/>
       <c r="B33" s="8"/>
       <c r="C33" s="14"/>
@@ -2691,7 +2693,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="16"/>
@@ -2736,7 +2738,7 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="15">
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A35" s="5"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
@@ -2781,54 +2783,59 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" customFormat="1"/>
-    <row r="37" spans="1:43" customFormat="1"/>
-    <row r="38" spans="1:43" customFormat="1"/>
-    <row r="39" spans="1:43" customFormat="1"/>
-    <row r="40" spans="1:43" customFormat="1"/>
-    <row r="41" spans="1:43" customFormat="1"/>
-    <row r="42" spans="1:43" customFormat="1"/>
-    <row r="43" spans="1:43" customFormat="1"/>
-    <row r="44" spans="1:43" customFormat="1"/>
-    <row r="45" spans="1:43" customFormat="1"/>
-    <row r="46" spans="1:43" customFormat="1"/>
-    <row r="47" spans="1:43" customFormat="1"/>
-    <row r="48" spans="1:43" customFormat="1"/>
-    <row r="49" customFormat="1"/>
-    <row r="50" customFormat="1"/>
-    <row r="51" customFormat="1"/>
-    <row r="52" customFormat="1"/>
-    <row r="53" customFormat="1"/>
-    <row r="54" customFormat="1"/>
-    <row r="55" customFormat="1"/>
-    <row r="56" customFormat="1"/>
-    <row r="57" customFormat="1"/>
-    <row r="58" customFormat="1"/>
-    <row r="59" customFormat="1"/>
-    <row r="60" customFormat="1"/>
-    <row r="61" customFormat="1"/>
-    <row r="62" customFormat="1"/>
-    <row r="63" customFormat="1"/>
-    <row r="64" customFormat="1"/>
-    <row r="65" customFormat="1"/>
-    <row r="66" customFormat="1"/>
-    <row r="67" customFormat="1"/>
-    <row r="68" customFormat="1"/>
-    <row r="69" customFormat="1"/>
-    <row r="70" customFormat="1"/>
-    <row r="71" customFormat="1"/>
-    <row r="72" customFormat="1"/>
-    <row r="73" customFormat="1"/>
-    <row r="74" customFormat="1"/>
-    <row r="75" customFormat="1"/>
-    <row r="76" customFormat="1"/>
-    <row r="77" customFormat="1"/>
-    <row r="78" customFormat="1"/>
-    <row r="79" customFormat="1"/>
-    <row r="80" customFormat="1"/>
-    <row r="81" customFormat="1"/>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2836,11 +2843,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
